--- a/110-creation-exemples/ig/StructureDefinition-as-dr-practitionerrole.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dr-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:21:44+00:00</t>
+    <t>2024-07-01T16:22:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-dr-practitionerrole.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dr-practitionerrole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-01T16:22:22+00:00</t>
+    <t>2024-07-02T08:22:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -878,7 +878,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>http://rpps.fr</t>
+    <t>https://rpps.esante.gouv.fr</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -1012,7 +1012,7 @@
     <t>PractitionerRole.identifier:numeroAm.system</t>
   </si>
   <si>
-    <t>http://ameli.fr</t>
+    <t>https://www.ameli.fr</t>
   </si>
   <si>
     <t>PractitionerRole.identifier:numeroAm.value</t>
@@ -1105,8 +1105,8 @@
     <t>Period.start</t>
   </si>
   <si>
-    <t xml:space="preserve">per-1
-</t>
+    <t>ele-1
+per-1</t>
   </si>
   <si>
     <t>dateDebutActivite</t>
@@ -7412,7 +7412,7 @@
         <v>80</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>119</v>
@@ -7424,7 +7424,7 @@
         <v>78</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>78</v>

--- a/110-creation-exemples/ig/StructureDefinition-as-dr-practitionerrole.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dr-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T08:22:21+00:00</t>
+    <t>2024-07-02T09:45:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-dr-practitionerrole.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dr-practitionerrole.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2998" uniqueCount="497">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2998" uniqueCount="502">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T09:45:37+00:00</t>
+    <t>2024-07-02T11:34:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -994,7 +994,7 @@
     <t>[Donnée restreinte] : Identifiant d’activité propre à l’Assurance Maladie. format: 9 digits. synonyme: numeroAM</t>
   </si>
   <si>
-    <t>numeroAM</t>
+    <t>SituationExercice.numeroAM</t>
   </si>
   <si>
     <t>PractitionerRole.identifier:numeroAm.id</t>
@@ -1109,7 +1109,7 @@
 per-1</t>
   </si>
   <si>
-    <t>dateDebutActivite</t>
+    <t>SituationExercice.dateDebutActivite</t>
   </si>
   <si>
     <t>DR.1</t>
@@ -1136,7 +1136,7 @@
     <t>Period.end</t>
   </si>
   <si>
-    <t>dateFinActivite</t>
+    <t>SituationExercice.dateFinActivite</t>
   </si>
   <si>
     <t>DR.2</t>
@@ -1217,6 +1217,9 @@
     <t>https://mos.esante.gouv.fr/NOS/JDV_J94-GenreActivite-RASS/FHIR/JDV-J94-GenreActivite-RASS</t>
   </si>
   <si>
+    <t>SituationExercice.genreActivite</t>
+  </si>
+  <si>
     <t>PractitionerRole.code:modeExercice</t>
   </si>
   <si>
@@ -1229,6 +1232,9 @@
     <t>https://mos.esante.gouv.fr/NOS/JDV_J95-ModeExercice-RASS/FHIR/JDV-J95-ModeExercice-RASS</t>
   </si>
   <si>
+    <t>SituationExercice.modeExercice</t>
+  </si>
+  <si>
     <t>PractitionerRole.code:typeActiviteLiberale</t>
   </si>
   <si>
@@ -1241,6 +1247,9 @@
     <t>https://mos.esante.gouv.fr/NOS/JDV_J96-TypeActiviteLiberale-RASS/FHIR/JDV-J96-TypeActiviteLiberale-RASS</t>
   </si>
   <si>
+    <t>SituationExercice.typeActiviteLiberale</t>
+  </si>
+  <si>
     <t>PractitionerRole.code:statutProfessionnelSSA</t>
   </si>
   <si>
@@ -1253,7 +1262,7 @@
     <t>https://mos.esante.gouv.fr/NOS/JDV_J97-StatutProfessionnelSSA-RASS/FHIR/JDV-J97-StatutProfessionnelSSA-RASS</t>
   </si>
   <si>
-    <t>statutPS_SSA</t>
+    <t>SituationExercice.statutPS_SSA</t>
   </si>
   <si>
     <t>PractitionerRole.code:statutHospitalier</t>
@@ -1268,6 +1277,9 @@
     <t>https://mos.esante.gouv.fr/NOS/JDV_J98-StatutHospitalier-RASS/FHIR/JDV-J98-StatutHospitalier-RASS</t>
   </si>
   <si>
+    <t>SituationExercice.statutHospitalier</t>
+  </si>
+  <si>
     <t>PractitionerRole.code:fonction</t>
   </si>
   <si>
@@ -1280,7 +1292,7 @@
     <t>https://mos.esante.gouv.fr/NOS/JDV_J108-EnsembleFonction-RASS/FHIR/JDV-J108-EnsembleFonction-RASS</t>
   </si>
   <si>
-    <t>role</t>
+    <t>SituationExercice.role</t>
   </si>
   <si>
     <t>PractitionerRole.code:metierPharmacien</t>
@@ -1293,6 +1305,9 @@
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J73-MetierPharmacien-RASS/FHIR/JDV-J73-MetierPharmacien-RASS</t>
+  </si>
+  <si>
+    <t>SituationExercice.metierPharmacien</t>
   </si>
   <si>
     <t>PractitionerRole.specialty</t>
@@ -1381,7 +1396,7 @@
 ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
   </si>
   <si>
-    <t>telecommunication</t>
+    <t>SituationExercice.telecommunication</t>
   </si>
   <si>
     <t>XTN</t>
@@ -1406,7 +1421,7 @@
     <t>BALs MSS de type PER rattachés à l'identifiant du professionnel de santé  ainsi qu'au lieu de sa situation d'exercice (BoiteLettreMSS).</t>
   </si>
   <si>
-    <t>boiteLettresMSS</t>
+    <t>SituationExercice.boiteLettresMSS</t>
   </si>
   <si>
     <t>PractitionerRole.availableTime</t>
@@ -8118,7 +8133,7 @@
         <v>102</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>380</v>
@@ -8135,13 +8150,13 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B54" t="s" s="2">
         <v>373</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D54" t="s" s="2">
         <v>78</v>
@@ -8166,7 +8181,7 @@
         <v>261</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M54" t="s" s="2">
         <v>375</v>
@@ -8204,7 +8219,7 @@
       </c>
       <c r="Y54" s="2"/>
       <c r="Z54" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>78</v>
@@ -8237,7 +8252,7 @@
         <v>102</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>380</v>
@@ -8254,13 +8269,13 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B55" t="s" s="2">
         <v>373</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="D55" t="s" s="2">
         <v>78</v>
@@ -8285,7 +8300,7 @@
         <v>261</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="M55" t="s" s="2">
         <v>375</v>
@@ -8323,7 +8338,7 @@
       </c>
       <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>78</v>
@@ -8356,7 +8371,7 @@
         <v>102</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>380</v>
@@ -8373,13 +8388,13 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B56" t="s" s="2">
         <v>373</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>78</v>
@@ -8404,7 +8419,7 @@
         <v>261</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="M56" t="s" s="2">
         <v>375</v>
@@ -8442,7 +8457,7 @@
       </c>
       <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>78</v>
@@ -8475,7 +8490,7 @@
         <v>102</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>380</v>
@@ -8492,13 +8507,13 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="B57" t="s" s="2">
         <v>373</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="D57" t="s" s="2">
         <v>78</v>
@@ -8523,7 +8538,7 @@
         <v>261</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="M57" t="s" s="2">
         <v>375</v>
@@ -8561,7 +8576,7 @@
       </c>
       <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>78</v>
@@ -8594,7 +8609,7 @@
         <v>102</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>380</v>
@@ -8611,13 +8626,13 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="B58" t="s" s="2">
         <v>373</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="D58" t="s" s="2">
         <v>78</v>
@@ -8642,7 +8657,7 @@
         <v>261</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="M58" t="s" s="2">
         <v>375</v>
@@ -8680,7 +8695,7 @@
       </c>
       <c r="Y58" s="2"/>
       <c r="Z58" t="s" s="2">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>78</v>
@@ -8713,7 +8728,7 @@
         <v>102</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>380</v>
@@ -8730,13 +8745,13 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="B59" t="s" s="2">
         <v>373</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="D59" t="s" s="2">
         <v>78</v>
@@ -8761,7 +8776,7 @@
         <v>261</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="M59" t="s" s="2">
         <v>375</v>
@@ -8799,7 +8814,7 @@
       </c>
       <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>78</v>
@@ -8832,7 +8847,7 @@
         <v>102</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>380</v>
@@ -8849,10 +8864,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8878,10 +8893,10 @@
         <v>261</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8912,7 +8927,7 @@
       </c>
       <c r="Y60" s="2"/>
       <c r="Z60" t="s" s="2">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>78</v>
@@ -8930,7 +8945,7 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -8948,13 +8963,13 @@
         <v>78</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>78</v>
@@ -8962,10 +8977,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8988,13 +9003,13 @@
         <v>91</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9045,7 +9060,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9066,21 +9081,21 @@
         <v>78</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>425</v>
+        <v>430</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9103,13 +9118,13 @@
         <v>78</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9160,7 +9175,7 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9178,10 +9193,10 @@
         <v>78</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>78</v>
@@ -9192,10 +9207,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9218,17 +9233,17 @@
         <v>78</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>78</v>
@@ -9265,7 +9280,7 @@
         <v>78</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="AC63" s="2"/>
       <c r="AD63" t="s" s="2">
@@ -9275,7 +9290,7 @@
         <v>117</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9287,19 +9302,19 @@
         <v>209</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>78</v>
@@ -9307,13 +9322,13 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="D64" t="s" s="2">
         <v>78</v>
@@ -9335,17 +9350,17 @@
         <v>78</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>78</v>
@@ -9394,7 +9409,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9406,19 +9421,19 @@
         <v>209</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="AK64" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="AN64" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>442</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>78</v>
@@ -9426,10 +9441,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9452,16 +9467,16 @@
         <v>78</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9511,7 +9526,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9532,7 +9547,7 @@
         <v>78</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>78</v>
@@ -9543,10 +9558,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9658,10 +9673,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9775,14 +9790,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -9804,10 +9819,10 @@
         <v>111</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="N68" t="s" s="2">
         <v>114</v>
@@ -9862,7 +9877,7 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -9894,10 +9909,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9923,10 +9938,10 @@
         <v>176</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9956,10 +9971,10 @@
         <v>254</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>78</v>
@@ -9977,7 +9992,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -9998,7 +10013,7 @@
         <v>78</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>78</v>
@@ -10009,10 +10024,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10038,10 +10053,10 @@
         <v>325</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10092,7 +10107,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10113,7 +10128,7 @@
         <v>78</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>78</v>
@@ -10124,10 +10139,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10150,16 +10165,16 @@
         <v>78</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10209,7 +10224,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10230,7 +10245,7 @@
         <v>78</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>78</v>
@@ -10241,10 +10256,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10267,16 +10282,16 @@
         <v>78</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10326,7 +10341,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10347,7 +10362,7 @@
         <v>78</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>78</v>
@@ -10358,10 +10373,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10384,13 +10399,13 @@
         <v>78</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10441,7 +10456,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10462,7 +10477,7 @@
         <v>78</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>78</v>
@@ -10473,10 +10488,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10588,10 +10603,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10705,14 +10720,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -10734,10 +10749,10 @@
         <v>111</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>114</v>
@@ -10792,7 +10807,7 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -10824,10 +10839,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10853,10 +10868,10 @@
         <v>104</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -10907,7 +10922,7 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>90</v>
@@ -10939,10 +10954,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10968,10 +10983,10 @@
         <v>294</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11022,7 +11037,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -11043,7 +11058,7 @@
         <v>78</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>78</v>
@@ -11054,10 +11069,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11083,10 +11098,10 @@
         <v>104</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11137,7 +11152,7 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -11158,7 +11173,7 @@
         <v>78</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>78</v>
@@ -11169,10 +11184,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11195,17 +11210,17 @@
         <v>78</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>78</v>
@@ -11254,7 +11269,7 @@
         <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>

--- a/110-creation-exemples/ig/StructureDefinition-as-dr-practitionerrole.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dr-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T11:34:04+00:00</t>
+    <t>2024-07-02T11:51:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1195,7 +1195,7 @@
     <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-practitioner-role-exercice</t>
   </si>
   <si>
-    <t xml:space="preserve">value:coding.system}
+    <t xml:space="preserve">pattern:$this}
 </t>
   </si>
   <si>

--- a/110-creation-exemples/ig/StructureDefinition-as-dr-practitionerrole.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dr-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T11:51:09+00:00</t>
+    <t>2024-07-02T12:01:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-dr-practitionerrole.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dr-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T12:01:26+00:00</t>
+    <t>2024-07-02T12:28:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-dr-practitionerrole.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dr-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T12:28:16+00:00</t>
+    <t>2024-07-02T14:06:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-dr-practitionerrole.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dr-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T14:06:23+00:00</t>
+    <t>2024-07-09T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-dr-practitionerrole.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dr-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T09:28:43+00:00</t>
+    <t>2024-07-09T09:35:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
